--- a/vtiger-crm-a12/src/test/resources/testScriptData.xlsx
+++ b/vtiger-crm-a12/src/test/resources/testScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohit Sharma\git\Vtiger-crm-fw\vtiger-crm-a12\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88666E5-5CB8-4B25-A749-46188FE2B2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F062EC-DDBE-4C86-B527-E18486493633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FavCar" sheetId="1" r:id="rId1"/>
@@ -193,9 +193,6 @@
     <t>9817500006</t>
   </si>
   <si>
-    <t>roy</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -245,6 +242,9 @@
   </si>
   <si>
     <t>GOOGLE</t>
+  </si>
+  <si>
+    <t>roy2</t>
   </si>
 </sst>
 </file>
@@ -999,7 +999,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -1126,10 +1126,10 @@
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -1137,10 +1137,10 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1176,56 +1176,56 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="12"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -1258,14 +1258,14 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="14"/>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="14"/>
